--- a/frontend/public/plantilla-alumnos.xlsx
+++ b/frontend/public/plantilla-alumnos.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t xml:space="preserve">DNI</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t xml:space="preserve">   Si la celda queda vacía o el valor no es válido, se importa como secundaria.</t>
+  </si>
+  <si>
+    <t>9. Las columnas Instancia, Titulo y Escuela tienen listas desplegables: elegí un valor de la lista. Si escribís otro valor, Excel advierte pero permite continuar.</t>
   </si>
 </sst>
 </file>
@@ -439,20 +442,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col customWidth="true" max="1" min="1" style="1" width="12"/>
+    <col customWidth="true" max="2" min="2" style="1" width="28"/>
+    <col customWidth="true" max="3" min="3" style="1" width="20"/>
+    <col customWidth="true" max="4" min="4" style="1" width="18"/>
+    <col customWidth="true" max="5" min="5" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -470,13 +473,21 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <dataValidations count="3">
+    <dataValidation allowBlank="true" error="El valor no está en la lista sugerida. Podés continuar igual, pero verificá que esté bien escrito." errorStyle="warning" errorTitle="Valor fuera de la lista" prompt="Desplegá la lista y elegí un valor. Si escribís otro valor, Excel advierte pero permite continuar." promptTitle="Elegí una opción" showErrorMessage="true" showInputMessage="true" sqref="C2:C1000" type="list">
+      <formula1>"Primera,Segunda,Tercera,Cuarta"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="El valor no está en la lista sugerida. Podés continuar igual, pero verificá que esté bien escrito." errorStyle="warning" errorTitle="Valor fuera de la lista" prompt="Desplegá la lista y elegí un valor. Si escribís otro valor, Excel advierte pero permite continuar." promptTitle="Elegí una opción" showErrorMessage="true" showInputMessage="true" sqref="D2:D1000" type="list">
+      <formula1>"Discapacidad,Hermanos/as,Hijos/as del personal,Origen a 300 m,Federados (Ed. Física),Cercanía del domicilio,Abanderados y escoltas titulares"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="El valor no está en la lista sugerida. Podés continuar igual, pero verificá que esté bien escrito." errorStyle="warning" errorTitle="Valor fuera de la lista" prompt="Desplegá la lista y elegí un valor. Si escribís otro valor, Excel advierte pero permite continuar." promptTitle="Elegí una opción" showErrorMessage="true" showInputMessage="true" sqref="E2:E1000" type="list">
+      <formula1>"secundaria,deportiva"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions gridLinesSet="true"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup cellComments="none" copies="1" fitToHeight="1" fitToWidth="1" horizontalDpi="300" orientation="portrait" pageOrder="downThenOver" paperSize="9" scale="100" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -552,6 +563,11 @@
         <v>16</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLinesSet="true"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
